--- a/StructureDefinition-open-elis-specimen.xlsx
+++ b/StructureDefinition-open-elis-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T15:46:49+00:00</t>
+    <t>2026-03-23T16:01:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -617,7 +617,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>https://demo.openelis-global.org/sampleItem_uuid</t>
+    <t>http://openelis-global.org/sampleItem_uuid</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>

--- a/StructureDefinition-open-elis-specimen.xlsx
+++ b/StructureDefinition-open-elis-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T16:01:57+00:00</t>
+    <t>2026-05-11T11:00:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-open-elis-specimen.xlsx
+++ b/StructureDefinition-open-elis-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T11:00:24+00:00</t>
+    <t>2026-05-11T11:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
